--- a/catalogo-produtos/importador/produtos-sem-codigo.xlsx
+++ b/catalogo-produtos/importador/produtos-sem-codigo.xlsx
@@ -46,7 +46,7 @@
     <t/>
   </si>
   <si>
-    <t>não</t>
+    <t>sim</t>
   </si>
   <si>
     <t>81c3ae11-51f6-4206-b328-e0e6607bb38a</t>
